--- a/storage/app/private/CLIENTES/BERNARDO/Bitacora_BERNARDO_ENERO-2026.xlsx
+++ b/storage/app/private/CLIENTES/BERNARDO/Bitacora_BERNARDO_ENERO-2026.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="104">
   <si>
     <t>Facturas De Bernardo</t>
   </si>
@@ -325,6 +325,9 @@
   </si>
   <si>
     <t>MONTO</t>
+  </si>
+  <si>
+    <t>NO</t>
   </si>
 </sst>
 </file>
@@ -2078,7 +2081,9 @@
       <c r="B5" s="6"/>
       <c r="C5" s="5"/>
       <c r="D5" s="7"/>
-      <c r="E5" s="6"/>
+      <c r="E5" s="6" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="8">
@@ -2087,7 +2092,9 @@
       <c r="B6" s="9"/>
       <c r="C6" s="8"/>
       <c r="D6" s="10"/>
-      <c r="E6" s="9"/>
+      <c r="E6" s="9" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5">
@@ -2096,7 +2103,9 @@
       <c r="B7" s="6"/>
       <c r="C7" s="5"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="6"/>
+      <c r="E7" s="6" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="8">
@@ -2105,7 +2114,9 @@
       <c r="B8" s="9"/>
       <c r="C8" s="8"/>
       <c r="D8" s="10"/>
-      <c r="E8" s="9"/>
+      <c r="E8" s="9" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="5">
@@ -2114,7 +2125,9 @@
       <c r="B9" s="6"/>
       <c r="C9" s="5"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="6"/>
+      <c r="E9" s="6" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="8">
@@ -2123,7 +2136,9 @@
       <c r="B10" s="9"/>
       <c r="C10" s="8"/>
       <c r="D10" s="10"/>
-      <c r="E10" s="9"/>
+      <c r="E10" s="9" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="11" spans="1:5">
       <c r="C11" s="11" t="s">
